--- a/REGISTRO_Y_ASISTENCIA_SIMPOSIO.xlsx
+++ b/REGISTRO_Y_ASISTENCIA_SIMPOSIO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -788,6 +788,94 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-0267</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Victor Julio</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>victor.julio267@correo-simulado.edu.gt</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>25042948</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-10-08 22:20:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-0079</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cristhian De León Pérez</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cristhian.perez079@correo-simulado.edu.gt</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>25042515</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-10-08 22:24:36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/REGISTRO_Y_ASISTENCIA_SIMPOSIO.xlsx
+++ b/REGISTRO_Y_ASISTENCIA_SIMPOSIO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -876,6 +876,50 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-0297</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Luis Jose Gomez</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>luis.gomez297@correo-simulado.edu.gt</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>25042982</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-10-08 22:51:28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
